--- a/PSG_Informed_RIASEC_Classification.xlsx
+++ b/PSG_Informed_RIASEC_Classification.xlsx
@@ -10,7 +10,7 @@
     <sheet r:id="rId1" sheetId="1" name="Program Classification"/>
     <sheet r:id="rId2" sheetId="2" name="RIASEC Basis"/>
     <sheet r:id="rId3" sheetId="3" name="Consolidated Codes"/>
-    <sheet r:id="rId4" sheetId="4" name="Methodology &amp;amp; Sources"/>
+    <sheet r:id="rId4" sheetId="4" name="Methodology &amp;amp;amp; Sources"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -462,7 +462,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -484,6 +484,12 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFffffff"/>
@@ -493,7 +499,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Carlito"/>
       <family val="2"/>
     </font>
@@ -574,28 +580,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general" wrapText="1"/>
@@ -603,22 +615,19 @@
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -985,66 +994,66 @@
   <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="8" width="34.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="22.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="8" width="11.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="8" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="48.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="8" width="52.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="8" width="28.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="10" width="34.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="10" width="22.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="10" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="10" width="11.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="10" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="10" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="10" width="48.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="10" width="52.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="10" width="28.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="27.95">
-      <c r="A1" s="13" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="22.5" customFormat="1" s="1">
+      <c r="A1" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="33.95" customFormat="1" s="3">
-      <c r="A2" s="14" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A2" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="33.95" customFormat="1" s="3">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="33.95" customFormat="1" s="3">
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="32.25" customFormat="1" s="1">
       <c r="A5" s="6" t="s">
         <v>44</v>
       </c>
@@ -1073,7 +1082,7 @@
         <v>107</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="116.25" customFormat="1" s="1">
       <c r="A6" s="7" t="s">
         <v>50</v>
       </c>
@@ -1102,7 +1111,7 @@
         <v>110</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="102.75" customFormat="1" s="1">
       <c r="A7" s="7" t="s">
         <v>10</v>
       </c>
@@ -1131,7 +1140,7 @@
         <v>113</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="88.5" customFormat="1" s="1">
       <c r="A8" s="7" t="s">
         <v>14</v>
       </c>
@@ -1160,7 +1169,7 @@
         <v>116</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="102.75" customFormat="1" s="1">
       <c r="A9" s="7" t="s">
         <v>18</v>
       </c>
@@ -1189,7 +1198,7 @@
         <v>119</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="84.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="102.75" customFormat="1" s="1">
       <c r="A10" s="7" t="s">
         <v>61</v>
       </c>
@@ -1218,7 +1227,7 @@
         <v>122</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="84.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="84.75" customFormat="1" s="1">
       <c r="A11" s="7" t="s">
         <v>63</v>
       </c>
@@ -1247,7 +1256,7 @@
         <v>125</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="84.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="84.75" customFormat="1" s="1">
       <c r="A12" s="7" t="s">
         <v>66</v>
       </c>
@@ -1276,7 +1285,7 @@
         <v>128</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="72" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="72" customFormat="1" s="1">
       <c r="A13" s="7" t="s">
         <v>68</v>
       </c>
@@ -1305,7 +1314,7 @@
         <v>131</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="72" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="72" customFormat="1" s="1">
       <c r="A14" s="7" t="s">
         <v>70</v>
       </c>
@@ -1334,7 +1343,7 @@
         <v>131</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="84.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="84.75" customFormat="1" s="1">
       <c r="A15" s="7" t="s">
         <v>71</v>
       </c>
@@ -1363,7 +1372,7 @@
         <v>136</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="84.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="84.75" customFormat="1" s="1">
       <c r="A16" s="7" t="s">
         <v>73</v>
       </c>
@@ -1392,7 +1401,7 @@
         <v>139</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="84.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="84.75" customFormat="1" s="1">
       <c r="A17" s="7" t="s">
         <v>36</v>
       </c>
@@ -1421,7 +1430,7 @@
         <v>142</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="58.5" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="58.5" customFormat="1" s="1">
       <c r="A18" s="7" t="s">
         <v>39</v>
       </c>
@@ -1444,22 +1453,22 @@
         <v>145</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1481,27 +1490,27 @@
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="12" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="13" width="10.005" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="8" width="18.005" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="8" width="48.005" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="8" width="58.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A1" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="10"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="30" customFormat="1" s="3">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A2" s="11"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="30" customFormat="1" s="1">
       <c r="A3" s="6" t="s">
         <v>79</v>
       </c>
@@ -1515,8 +1524,8 @@
         <v>82</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="50.1" customFormat="1" s="3">
-      <c r="A4" s="11" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="50.1" customFormat="1" s="1">
+      <c r="A4" s="12" t="s">
         <v>58</v>
       </c>
       <c r="B4" s="7" t="s">
@@ -1529,8 +1538,8 @@
         <v>85</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="50.1" customFormat="1" s="3">
-      <c r="A5" s="11" t="s">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="50.1" customFormat="1" s="1">
+      <c r="A5" s="12" t="s">
         <v>53</v>
       </c>
       <c r="B5" s="7" t="s">
@@ -1543,8 +1552,8 @@
         <v>88</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="50.1" customFormat="1" s="3">
-      <c r="A6" s="11" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="50.1" customFormat="1" s="1">
+      <c r="A6" s="12" t="s">
         <v>64</v>
       </c>
       <c r="B6" s="7" t="s">
@@ -1557,8 +1566,8 @@
         <v>91</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="50.1" customFormat="1" s="3">
-      <c r="A7" s="11" t="s">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="50.1" customFormat="1" s="1">
+      <c r="A7" s="12" t="s">
         <v>56</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -1571,8 +1580,8 @@
         <v>94</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="50.1" customFormat="1" s="3">
-      <c r="A8" s="11" t="s">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="50.1" customFormat="1" s="1">
+      <c r="A8" s="12" t="s">
         <v>51</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -1585,8 +1594,8 @@
         <v>97</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="50.1" customFormat="1" s="3">
-      <c r="A9" s="11" t="s">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="50.1" customFormat="1" s="1">
+      <c r="A9" s="12" t="s">
         <v>52</v>
       </c>
       <c r="B9" s="7" t="s">
@@ -1618,33 +1627,33 @@
   <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="8" width="38.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="11.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="8" width="11.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="8" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="34.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="10" width="38.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="10" width="11.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="10" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="10" width="11.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="10" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="10" width="34.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="30" customFormat="1" s="3">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="30" customFormat="1" s="1">
       <c r="A3" s="6" t="s">
         <v>44</v>
       </c>
@@ -1664,7 +1673,7 @@
         <v>49</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A4" s="7" t="s">
         <v>50</v>
       </c>
@@ -1684,7 +1693,7 @@
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A5" s="7" t="s">
         <v>10</v>
       </c>
@@ -1704,7 +1713,7 @@
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A6" s="7" t="s">
         <v>14</v>
       </c>
@@ -1724,7 +1733,7 @@
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A7" s="7" t="s">
         <v>18</v>
       </c>
@@ -1744,7 +1753,7 @@
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A8" s="7" t="s">
         <v>61</v>
       </c>
@@ -1764,7 +1773,7 @@
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A9" s="7" t="s">
         <v>63</v>
       </c>
@@ -1784,7 +1793,7 @@
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A10" s="7" t="s">
         <v>66</v>
       </c>
@@ -1804,7 +1813,7 @@
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A11" s="7" t="s">
         <v>68</v>
       </c>
@@ -1824,7 +1833,7 @@
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A12" s="7" t="s">
         <v>70</v>
       </c>
@@ -1844,7 +1853,7 @@
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A13" s="7" t="s">
         <v>71</v>
       </c>
@@ -1864,7 +1873,7 @@
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A14" s="7" t="s">
         <v>73</v>
       </c>
@@ -1884,7 +1893,7 @@
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A15" s="7" t="s">
         <v>36</v>
       </c>
@@ -1904,11 +1913,11 @@
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A16" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="2"/>
+      <c r="B16" s="3"/>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9" t="s">
@@ -1918,15 +1927,15 @@
         <v>76</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A17" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1953,21 +1962,21 @@
     <col min="4" max="4" style="8" width="28.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="27.95" customFormat="1" s="3">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -1975,31 +1984,31 @@
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="30" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="30" customFormat="1" s="1">
       <c r="A8" s="6" t="s">
         <v>2</v>
       </c>
@@ -2013,7 +2022,7 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A9" s="7" t="s">
         <v>6</v>
       </c>
@@ -2027,7 +2036,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A10" s="7" t="s">
         <v>10</v>
       </c>
@@ -2041,7 +2050,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A11" s="7" t="s">
         <v>14</v>
       </c>
@@ -2055,7 +2064,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A12" s="7" t="s">
         <v>18</v>
       </c>
@@ -2069,7 +2078,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A13" s="7" t="s">
         <v>21</v>
       </c>
@@ -2083,7 +2092,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A14" s="7" t="s">
         <v>24</v>
       </c>
@@ -2097,7 +2106,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A15" s="7" t="s">
         <v>27</v>
       </c>
@@ -2111,7 +2120,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A16" s="7" t="s">
         <v>30</v>
       </c>
@@ -2125,7 +2134,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A17" s="7" t="s">
         <v>33</v>
       </c>
@@ -2139,7 +2148,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A18" s="7" t="s">
         <v>36</v>
       </c>
@@ -2153,7 +2162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="27.95" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="27.95" customFormat="1" s="1">
       <c r="A19" s="7" t="s">
         <v>39</v>
       </c>
